--- a/daily_matches/job_matches_2026-04-13.xlsx
+++ b/daily_matches/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect, ML/AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DoiT</t>
+          <t>SwapsTech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3, Glue, Redshift</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, MySQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7df305cb5baa7b</t>
+          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GenAI Data Scientist, Commercial, Supply Chain &amp; Trading</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,112 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2519af0b61a9f3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>AI Context Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Robert Half</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, Glue, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sr. AI &amp; Data Science Analyst</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kedrion Biopharma</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fort Lee, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7168e60aa12e407a</t>
+          <t>https://www.indeed.com/viewjob?jk=f84c1822d5830ffb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-13.xlsx
+++ b/daily_matches/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SwapsTech</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, MySQL, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Inqud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=eff66a4b2084d643</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Context Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f84c1822d5830ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=80210b89b5ac23a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b66ee737929a38da</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-13.xlsx
+++ b/daily_matches/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Prompt Engineering, TensorFlow, PyTorch, S3, Redshift, MLflow, FastAPI, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Software Engineer II, Machine Learning</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Inqud</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, Redshift, Kinesis, MLflow, Docker, Kubernetes, Git, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff66a4b2084d643</t>
+          <t>https://www.indeed.com/viewjob?jk=97020b8d9d3117b5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Clinical Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Baylor Scott &amp; White Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Keras, CI/CD, Git, Snowflake, PySpark, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,252 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80210b89b5ac23a2</t>
+          <t>https://www.indeed.com/viewjob?jk=840cf219760297c3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mirion</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Kinesis, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Poshmark</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3770706b5e510729</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NAVA TECH LLC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, S3, EC2, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29085cf561343601</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Git, Snowflake, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b66ee737929a38da</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9da9855aff29b6b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0e3648f8e322ab4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Junior BI Developer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Enzo Tech Group</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Newtown Square, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63ab818b4f18638c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-13.xlsx
+++ b/daily_matches/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Prompt Engineering, TensorFlow, PyTorch, S3, Redshift, MLflow, FastAPI, Docker, Kubernetes, Jenkins</t>
+          <t>RAG, S3, Data Lake, Kubernetes, Terraform, Git, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II, Machine Learning</t>
+          <t>Applied AI Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, Redshift, Kinesis, MLflow, Docker, Kubernetes, Git, Redshift</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97020b8d9d3117b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab997fd1b22f1b7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clinical Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Baylor Scott &amp; White Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Keras, CI/CD, Git, Snowflake, PySpark, Python</t>
+          <t>Kubernetes, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840cf219760297c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d5c730a41756c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer - Artificial Intelligence Platform Team</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL</t>
+          <t>LangChain, RAG, LLaMA, Copilot, AKS, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf7f53f7fa0f650</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Platform</t>
+          <t>Technical Support Engineer II-Scores Software Team</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,46 +622,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Kinesis, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python, SQL</t>
+          <t>RAG, Prompt Engineering, S3, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
+          <t>https://www.indeed.com/viewjob?jk=06d799b72694d188</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>GTM Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>InvoiceCloud</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,147 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3770706b5e510729</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Jr. Data Scientist</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NAVA TECH LLC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, S3, EC2, Git, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29085cf561343601</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Precisely</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Generative AI, Copilot, Git, Snowflake, Databricks, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9da9855aff29b6b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Precisely</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e3648f8e322ab4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Junior BI Developer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Enzo Tech Group</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Newtown Square, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63ab818b4f18638c</t>
+          <t>https://www.indeed.com/viewjob?jk=e592443b1efad79e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-13.xlsx
+++ b/daily_matches/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Senior AWS Cloud Engineer - (US - Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Kubernetes, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>RAG, S3, EC2, Glue, Athena, Redshift, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=03406469e62daa61</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied AI Analyst</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R</t>
+          <t>S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab997fd1b22f1b7</t>
+          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>IHG Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d5c730a41756c</t>
+          <t>https://www.indeed.com/viewjob?jk=b46fc40141ef5f0d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Platform Engineer - Artificial Intelligence Platform Team</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, AKS, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf7f53f7fa0f650</t>
+          <t>https://www.indeed.com/viewjob?jk=592e30099e512b90</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technical Support Engineer II-Scores Software Team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Traba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,252 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d799b72694d188</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ff132712ccfde9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GTM Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>InvoiceCloud</t>
+          <t>Traba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6278d5200c1903fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Consultant - Artificial Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f955523ef0dfb00c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Automation Test Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technoviz LLC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1b06911e9e68933</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Associate Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FreshDirect</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Woodbridge, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e592443b1efad79e</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, MySQL, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d6a2b22df95c891</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Traba</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be9642915e59df4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>POOLCORP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Covington, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Kafka, Hadoop, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdef7c235b1898fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VyStar Credit Union</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc35e796041da158</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-13.xlsx
+++ b/daily_matches/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer - (US - Remote)</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Athena, Redshift, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, RAG, Copilot, S3, Glue, FastAPI, CI/CD, Git, Snowflake, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03406469e62daa61</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB</t>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, CI/CD, Git, Databricks, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
+          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IHG Hotels &amp; Resorts</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, NoSQL, Python</t>
+          <t>Generative AI, RAG, S3, EC2, Glue, Docker, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46fc40141ef5f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=90079673f1f3efb8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>Aegis Mobile</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Azure ML, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592e30099e512b90</t>
+          <t>https://www.indeed.com/viewjob?jk=9838baa40a1f085f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>QA Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ff132712ccfde9</t>
+          <t>https://www.indeed.com/viewjob?jk=50bac8ad190e44d1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Agentic Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6278d5200c1903fb</t>
+          <t>https://www.indeed.com/viewjob?jk=66ca2c3a4dfe0f91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Consultant - Artificial Intelligence Developer</t>
+          <t>AI &amp; Analytics Intern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Sonoco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartsville, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f955523ef0dfb00c</t>
+          <t>https://www.indeed.com/viewjob?jk=877b4f791483d654</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Automation Test Engineer</t>
+          <t>MS Fabrics Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Technoviz LLC</t>
+          <t>AI SPINS INC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>Copilot, Synapse, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b06911e9e68933</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a4b1377ab14a5e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Power BI Developer</t>
+          <t>ML Research Scientist / ML Engineer – Surgical Applications</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>EDDA Technology, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, MySQL, Power BI, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Keras, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6a2b22df95c891</t>
+          <t>https://www.indeed.com/viewjob?jk=99731c86636e3379</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Functional Senior Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9642915e59df4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7aaaaa61c7b63e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Functional Senior Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kafka, Hadoop, Power BI, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef7c235b1898fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c39ecda6a5534f2a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Production Support Engineer</t>
+          <t>AI Functional Senior Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VyStar Credit Union</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Power BI, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,1372 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc35e796041da158</t>
+          <t>https://www.indeed.com/viewjob?jk=d86bd33f6a179cfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Woodland Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96810aa860007d06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dacf8abef09665cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3c9377d1354026d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>South Bend, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6521cc896fc0f796</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>The Woodlands, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ba2858df081720</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c97b5900b8466851</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eac388e2a2ab5141</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d64c3c6588deeeb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c76ef3467df74d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89bcff9c5dcf0889</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Oakbrook Terrace, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d75544fc2710019</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93013a077d37cb7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3ece6fb81383e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Lexington, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=205ccbaa198137c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b9dc868beef4d9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8937af46fad4bc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc481dbe6dd81df8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b804551b80bc3c4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efe60fea58ae36ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Livingston, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0c6ecca5edc51f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Manchester, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=518acd6f08fcd35a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01b9c77cbeadea05</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7493c7ffa8d3f95c</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Elkhart, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b984ec98190ea08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Burlington, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9956448538f5d614</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cadc880d79c8cb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a53d447481e8a6c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=217ea60c8b199aa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc0716fdd1dce38e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc37e1cd0386e733</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4137a26471ccd6f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb046ec53feb72da</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=150a8ca486100d20</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f81d5dddf76730f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI Functional Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f490a09ccb942bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JFDI Accountants</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, MySQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae076503cb3dfeee</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6004e7f5a216536</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sciata</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=632ded91d405def2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0685d2dc90d8f798</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-13.xlsx
+++ b/daily_matches/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, S3, Glue, FastAPI, CI/CD, Git, Snowflake, PySpark</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4341508fe1c04f1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Data Architect (Hybrid)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, CI/CD, Git, Databricks, PySpark, Kafka, Python</t>
+          <t>RAG, Glue, Redshift, Kinesis, CI/CD, Terraform, Git, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0e64cf5300616c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Glue, Docker, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>Data Scientist, LangChain, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90079673f1f3efb8</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior, Data Scientist - Merchandising Analytics (Member and Insights)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aegis Mobile</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Azure ML, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Git, PySpark, NoSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9838baa40a1f085f</t>
+          <t>https://www.indeed.com/viewjob?jk=68c478dde219e6f5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QA Engineer II</t>
+          <t>Senior Backend / Systems Engineer (AI) - San Mateo, CA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Trustlab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Kubernetes, CI/CD, Snowflake, Python, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bac8ad190e44d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e0d17081511027c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Agentic Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, PyTorch, XGBoost, LightGBM, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ca2c3a4dfe0f91</t>
+          <t>https://www.indeed.com/viewjob?jk=f851acf551dfaca9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI &amp; Analytics Intern</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sonoco</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartsville, SC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Hypothesis Testing</t>
+          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Hadoop, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877b4f791483d654</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MS Fabrics Data Engineer</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AI SPINS INC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Synapse, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a4b1377ab14a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ML Research Scientist / ML Engineer – Surgical Applications</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EDDA Technology, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Keras, Python, R, Optimization</t>
+          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99731c86636e3379</t>
+          <t>https://www.indeed.com/viewjob?jk=5d2f2b3088f910b3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7aaaaa61c7b63e</t>
+          <t>https://www.indeed.com/viewjob?jk=f64d013bcc57d616</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39ecda6a5534f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ebc35e151ef300</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86bd33f6a179cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=9f75b248f5282055</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Senior Data Engineer ***EST Preferred</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96810aa860007d06</t>
+          <t>https://www.indeed.com/viewjob?jk=fff2ab5c79a1b89e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>AIA Contract Documents</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacf8abef09665cf</t>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Full-Stack Engineer (Mid-level)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c9377d1354026d</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e46626ac0d71da</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Copilot, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6521cc896fc0f796</t>
+          <t>https://www.indeed.com/viewjob?jk=5a98db9b16e998d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Senior Data Engineer ***EST Preferred</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ba2858df081720</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffeace833fb2888</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>CyberArk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97b5900b8466851</t>
+          <t>https://www.indeed.com/viewjob?jk=1b8179dd640da19f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Business Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>Data Scientist, BigQuery, Databricks, BigQuery, PySpark, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac388e2a2ab5141</t>
+          <t>https://www.indeed.com/viewjob?jk=0189f899c2cea879</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d64c3c6588deeeb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2fe1f90761c400d3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Langan Engineering and Environmental Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c76ef3467df74d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d580eab570f1da</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ECFX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89bcff9c5dcf0889</t>
+          <t>https://www.indeed.com/viewjob?jk=629af72bc30a01ff</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d75544fc2710019</t>
+          <t>https://www.indeed.com/viewjob?jk=310069a484a3ae31</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Git, Kafka, Cassandra, NoSQL, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93013a077d37cb7e</t>
+          <t>https://www.indeed.com/viewjob?jk=88a7844c66d74b9c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Git, Kafka, Cassandra, NoSQL, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ece6fb81383e53</t>
+          <t>https://www.indeed.com/viewjob?jk=2d09f2853c28f42f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Git, Kafka, Cassandra, NoSQL, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205ccbaa198137c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a28ca6bbe3d9139</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9dc868beef4d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b05b1b7d9b2b96b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Git, Kafka, Cassandra, NoSQL, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8937af46fad4bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=1d24aa4e7cf497a7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc481dbe6dd81df8</t>
+          <t>https://www.indeed.com/viewjob?jk=10716450c14b40ab</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>AI Automation Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b804551b80bc3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1af3c3d4ac9319</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe60fea58ae36ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Livingston, NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c6ecca5edc51f1</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Manchester, NH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518acd6f08fcd35a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b9c77cbeadea05</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Functional Senior Consultant</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,567 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7493c7ffa8d3f95c</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Elkhart, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b984ec98190ea08a</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Burlington, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9956448538f5d614</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cadc880d79c8cb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a53d447481e8a6c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=217ea60c8b199aa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc0716fdd1dce38e</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc37e1cd0386e733</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4137a26471ccd6f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Sarasota, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb046ec53feb72da</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=150a8ca486100d20</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f81d5dddf76730f</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AI Functional Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f490a09ccb942bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>JFDI Accountants</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, MySQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae076503cb3dfeee</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6004e7f5a216536</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Sciata</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=632ded91d405def2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Foster City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0685d2dc90d8f798</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
